--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.937183674180321</v>
+        <v>1.452292347054302</v>
       </c>
       <c r="D2" t="n">
-        <v>8.352766289681529</v>
+        <v>1.357324522073249</v>
       </c>
       <c r="E2" t="n">
-        <v>15.11852957256873</v>
+        <v>2.456761055542417</v>
       </c>
       <c r="F2" t="n">
-        <v>12.22339549002951</v>
+        <v>1.986301767129795</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.26535336795309</v>
+        <v>2.643119922292378</v>
       </c>
       <c r="D3" t="n">
-        <v>15.31979424720418</v>
+        <v>2.489466565170679</v>
       </c>
       <c r="E3" t="n">
-        <v>15.11852957256873</v>
+        <v>2.456761055542417</v>
       </c>
       <c r="F3" t="n">
-        <v>12.22339549002951</v>
+        <v>1.986301767129795</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.25504831083227</v>
+        <v>8.978945350510244</v>
       </c>
       <c r="D4" t="n">
-        <v>10.43456201743379</v>
+        <v>1.695616327832992</v>
       </c>
       <c r="E4" t="n">
-        <v>15.11852957256873</v>
+        <v>2.456761055542417</v>
       </c>
       <c r="F4" t="n">
-        <v>12.22339549002951</v>
+        <v>1.986301767129795</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.18354444387267</v>
+        <v>6.854825972129309</v>
       </c>
       <c r="D5" t="n">
-        <v>42.49054419694144</v>
+        <v>6.904713432002984</v>
       </c>
       <c r="E5" t="n">
-        <v>15.11852957256873</v>
+        <v>2.456761055542417</v>
       </c>
       <c r="F5" t="n">
-        <v>12.22339549002951</v>
+        <v>1.986301767129795</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.22602118717688</v>
+        <v>6.699228442916243</v>
       </c>
       <c r="D6" t="n">
-        <v>41.04683008069585</v>
+        <v>6.670109888113076</v>
       </c>
       <c r="E6" t="n">
-        <v>15.11852957256873</v>
+        <v>2.456761055542417</v>
       </c>
       <c r="F6" t="n">
-        <v>12.22339549002951</v>
+        <v>1.986301767129795</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.62966703815091</v>
+        <v>8.714820893699523</v>
       </c>
       <c r="D7" t="n">
-        <v>18.00368443017219</v>
+        <v>2.925598719902982</v>
       </c>
       <c r="E7" t="n">
-        <v>15.11852957256873</v>
+        <v>2.456761055542417</v>
       </c>
       <c r="F7" t="n">
-        <v>12.22339549002951</v>
+        <v>1.986301767129795</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>55.9577219558231</v>
+        <v>9.093129817821255</v>
       </c>
       <c r="D8" t="n">
-        <v>11.23610252712212</v>
+        <v>1.825866660657344</v>
       </c>
       <c r="E8" t="n">
-        <v>15.11852957256873</v>
+        <v>2.456761055542417</v>
       </c>
       <c r="F8" t="n">
-        <v>12.22339549002951</v>
+        <v>1.986301767129795</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.73076180994116</v>
+        <v>5.481248794115439</v>
       </c>
       <c r="D9" t="n">
-        <v>5.004526843087408</v>
+        <v>0.8132356120017038</v>
       </c>
       <c r="E9" t="n">
-        <v>15.11852957256873</v>
+        <v>2.456761055542417</v>
       </c>
       <c r="F9" t="n">
-        <v>12.22339549002951</v>
+        <v>1.986301767129795</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.29082260451475</v>
+        <v>6.547258673233648</v>
       </c>
       <c r="D10" t="n">
-        <v>16.99214760348999</v>
+        <v>2.761223985567123</v>
       </c>
       <c r="E10" t="n">
-        <v>15.11852957256873</v>
+        <v>2.456761055542417</v>
       </c>
       <c r="F10" t="n">
-        <v>12.22339549002951</v>
+        <v>1.986301767129795</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>27.21050072701863</v>
+        <v>4.421706368140528</v>
       </c>
       <c r="D11" t="n">
-        <v>27.28552729928451</v>
+        <v>4.433898186133733</v>
       </c>
       <c r="E11" t="n">
-        <v>15.11852957256873</v>
+        <v>2.456761055542417</v>
       </c>
       <c r="F11" t="n">
-        <v>12.22339549002951</v>
+        <v>1.986301767129795</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>48.91826497712098</v>
+        <v>7.949218058782161</v>
       </c>
       <c r="D12" t="n">
-        <v>31.34086788842964</v>
+        <v>5.092891031869817</v>
       </c>
       <c r="E12" t="n">
-        <v>15.11852957256873</v>
+        <v>2.456761055542417</v>
       </c>
       <c r="F12" t="n">
-        <v>12.22339549002951</v>
+        <v>1.986301767129795</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>51.94382649662144</v>
+        <v>8.440871805700985</v>
       </c>
       <c r="D13" t="n">
-        <v>4.47213595499958</v>
+        <v>0.7267220926874317</v>
       </c>
       <c r="E13" t="n">
-        <v>15.11852957256873</v>
+        <v>2.456761055542417</v>
       </c>
       <c r="F13" t="n">
-        <v>12.22339549002951</v>
+        <v>1.986301767129795</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>58.82881661033336</v>
+        <v>9.55968269917917</v>
       </c>
       <c r="D14" t="n">
-        <v>15.67476686162396</v>
+        <v>2.547149615013894</v>
       </c>
       <c r="E14" t="n">
-        <v>15.11852957256873</v>
+        <v>2.456761055542417</v>
       </c>
       <c r="F14" t="n">
-        <v>12.22339549002951</v>
+        <v>1.986301767129795</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
